--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.164.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.164.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.164" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.164" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.164.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.164.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0164.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0164.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -859,7 +859,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.164.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.164.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.164" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.164" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,28 +416,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="50" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -603,18 +603,18 @@
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Service of Papers with Subp Ã¦ na</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 35</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L4: isolated marker/symbol line :: 34</t>
@@ -622,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -632,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 35</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -669,7 +673,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L63: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 36â€”37</t>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 35</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -724,7 +728,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 36â€”37</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: 86—87 •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -762,7 +766,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -779,7 +783,7 @@
       <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: 86â€”87 â€¢</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -830,7 +834,7 @@
       <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -881,7 +885,7 @@
       <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -932,7 +936,7 @@
       <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: May be read against an Answer.•</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -983,7 +987,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L89: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: May be read against an Answer.â€¢</t>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -995,7 +999,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L58: symbol-only separator/garbage line :: . 35</t>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 35</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1017,12 +1021,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1034,7 +1038,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L96: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1046,7 +1050,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 35</t>
+          <t>L58: symbol-only separator/garbage line :: . 35</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1073,7 +1077,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1085,7 +1089,7 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1097,7 +1101,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L62: symbol-only separator/garbage line :: .36</t>
+          <t>L60: isolated marker/symbol line :: 35</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1124,7 +1128,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1134,11 +1138,7 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 113</t>
+          <t>L62: symbol-only separator/garbage line :: .36</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 113</t>
+          <t>L63: symbol-only separator/garbage line :: 36—37</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 139</t>
+          <t>L65: symbol-only separator/garbage line :: . 36—37</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: 154</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: 86—87 •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 85</t>
+          <t>L69: isolated marker/symbol line :: 113</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 85</t>
+          <t>L71: isolated marker/symbol line :: 113</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 105</t>
+          <t>L73: isolated marker/symbol line :: 139</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L75: isolated marker/symbol line :: 154</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L77: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L79: isolated marker/symbol line :: 85</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L81: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
       <c r="N23" s="1" t="inlineStr"/>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
       <c r="N24" s="1" t="inlineStr"/>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN | isolated marker/symbol line :: â‚¬</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1634,6 +1634,130 @@
       <c r="X24" s="1" t="inlineStr"/>
       <c r="Y24" s="1" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr"/>
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr"/>
+      <c r="D25" s="1" t="inlineStr"/>
+      <c r="E25" s="1" t="inlineStr"/>
+      <c r="F25" s="1" t="inlineStr"/>
+      <c r="G25" s="1" t="inlineStr"/>
+      <c r="H25" s="1" t="inlineStr"/>
+      <c r="I25" s="1" t="inlineStr"/>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
+      <c r="L25" s="1" t="inlineStr"/>
+      <c r="M25" s="1" t="inlineStr"/>
+      <c r="N25" s="1" t="inlineStr"/>
+      <c r="O25" s="1" t="inlineStr">
+        <is>
+          <t>L87: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P25" s="1" t="inlineStr"/>
+      <c r="Q25" s="1" t="inlineStr"/>
+      <c r="R25" s="1" t="inlineStr"/>
+      <c r="S25" s="1" t="inlineStr"/>
+      <c r="T25" s="1" t="inlineStr"/>
+      <c r="U25" s="1" t="inlineStr"/>
+      <c r="V25" s="1" t="inlineStr"/>
+      <c r="W25" s="1" t="inlineStr"/>
+      <c r="X25" s="1" t="inlineStr"/>
+      <c r="Y25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr"/>
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr"/>
+      <c r="D26" s="1" t="inlineStr"/>
+      <c r="E26" s="1" t="inlineStr"/>
+      <c r="F26" s="1" t="inlineStr"/>
+      <c r="G26" s="1" t="inlineStr"/>
+      <c r="H26" s="1" t="inlineStr"/>
+      <c r="I26" s="1" t="inlineStr"/>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
+      <c r="L26" s="1" t="inlineStr"/>
+      <c r="M26" s="1" t="inlineStr"/>
+      <c r="N26" s="1" t="inlineStr"/>
+      <c r="O26" s="1" t="inlineStr">
+        <is>
+          <t>L94: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P26" s="1" t="inlineStr"/>
+      <c r="Q26" s="1" t="inlineStr"/>
+      <c r="R26" s="1" t="inlineStr"/>
+      <c r="S26" s="1" t="inlineStr"/>
+      <c r="T26" s="1" t="inlineStr"/>
+      <c r="U26" s="1" t="inlineStr"/>
+      <c r="V26" s="1" t="inlineStr"/>
+      <c r="W26" s="1" t="inlineStr"/>
+      <c r="X26" s="1" t="inlineStr"/>
+      <c r="Y26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr"/>
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr"/>
+      <c r="D27" s="1" t="inlineStr"/>
+      <c r="E27" s="1" t="inlineStr"/>
+      <c r="F27" s="1" t="inlineStr"/>
+      <c r="G27" s="1" t="inlineStr"/>
+      <c r="H27" s="1" t="inlineStr"/>
+      <c r="I27" s="1" t="inlineStr"/>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
+      <c r="L27" s="1" t="inlineStr"/>
+      <c r="M27" s="1" t="inlineStr"/>
+      <c r="N27" s="1" t="inlineStr"/>
+      <c r="O27" s="1" t="inlineStr">
+        <is>
+          <t>L96: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P27" s="1" t="inlineStr"/>
+      <c r="Q27" s="1" t="inlineStr"/>
+      <c r="R27" s="1" t="inlineStr"/>
+      <c r="S27" s="1" t="inlineStr"/>
+      <c r="T27" s="1" t="inlineStr"/>
+      <c r="U27" s="1" t="inlineStr"/>
+      <c r="V27" s="1" t="inlineStr"/>
+      <c r="W27" s="1" t="inlineStr"/>
+      <c r="X27" s="1" t="inlineStr"/>
+      <c r="Y27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr"/>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr"/>
+      <c r="D28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr"/>
+      <c r="F28" s="1" t="inlineStr"/>
+      <c r="G28" s="1" t="inlineStr"/>
+      <c r="H28" s="1" t="inlineStr"/>
+      <c r="I28" s="1" t="inlineStr"/>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
+      <c r="L28" s="1" t="inlineStr"/>
+      <c r="M28" s="1" t="inlineStr"/>
+      <c r="N28" s="1" t="inlineStr"/>
+      <c r="O28" s="1" t="inlineStr">
+        <is>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: €</t>
+        </is>
+      </c>
+      <c r="P28" s="1" t="inlineStr"/>
+      <c r="Q28" s="1" t="inlineStr"/>
+      <c r="R28" s="1" t="inlineStr"/>
+      <c r="S28" s="1" t="inlineStr"/>
+      <c r="T28" s="1" t="inlineStr"/>
+      <c r="U28" s="1" t="inlineStr"/>
+      <c r="V28" s="1" t="inlineStr"/>
+      <c r="W28" s="1" t="inlineStr"/>
+      <c r="X28" s="1" t="inlineStr"/>
+      <c r="Y28" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
